--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
@@ -47,7 +47,7 @@
     <t>{dept}</t>
   </si>
   <si>
-    <t>{year}年{month}月{day}日</t>
+    <t>{yearMonthDay}</t>
   </si>
   <si>
     <t>财务收单编码：</t>
@@ -143,7 +143,7 @@
     <t>小写总计金额</t>
   </si>
   <si>
-    <t>{lowFeeTotal}</t>
+    <t>￥{lowFeeTotalQian}</t>
   </si>
   <si>
     <t>是否冲借支</t>
@@ -245,7 +245,7 @@
     <t>总计进项税额</t>
   </si>
   <si>
-    <t>{taxCostTotal}</t>
+    <t>￥{taxCostTotalQian}</t>
   </si>
   <si>
     <t>总计金额（大写）</t>
@@ -257,7 +257,7 @@
     <t>总计金额（小写）</t>
   </si>
   <si>
-    <t>{lowCostTotal}</t>
+    <t>￥{lowCostTotalQian}</t>
   </si>
 </sst>
 </file>
@@ -1641,7 +1641,7 @@
     <col min="9" max="9" width="8.875" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.5" style="1" customWidth="1"/>
     <col min="11" max="11" width="9.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16.875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="50.1" customHeight="1" spans="1:12">
@@ -2110,7 +2110,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2 B7:D7 B8:D8 B12"/>
   </dataValidations>
   <pageMargins left="0.776388888888889" right="0.776388888888889" top="0.776388888888889" bottom="0.776388888888889" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="56" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="55" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
@@ -1050,7 +1050,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1065,12 +1065,12 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1101,12 +1101,16 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1129,6 +1133,14 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1158,7 +1170,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1167,18 +1179,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1214,7 +1214,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1243,6 +1243,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1634,14 +1638,14 @@
     <col min="2" max="2" width="21.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="8.625" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.375" style="1" customWidth="1"/>
     <col min="8" max="8" width="8" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.875" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.5" style="1" customWidth="1"/>
     <col min="11" max="11" width="9.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="17.875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="19.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="50.1" customHeight="1" spans="1:12">
@@ -1757,31 +1761,31 @@
       <c r="B5" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="13" t="s">
         <v>32</v>
       </c>
       <c r="L5" s="41" t="s">
@@ -1789,18 +1793,18 @@
       </c>
     </row>
     <row r="6" ht="45" customHeight="1" spans="1:12">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="19"/>
       <c r="I6" s="42" t="s">
         <v>36</v>
       </c>
@@ -1811,7 +1815,7 @@
       <c r="L6" s="45"/>
     </row>
     <row r="7" ht="45" customHeight="1" spans="1:12">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="20" t="s">
         <v>38</v>
       </c>
       <c r="B7" s="12" t="s">
@@ -1822,11 +1826,11 @@
       <c r="E7" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="20"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="23"/>
       <c r="I7" s="7" t="s">
         <v>42</v>
       </c>
@@ -1837,7 +1841,7 @@
       <c r="L7" s="12"/>
     </row>
     <row r="8" ht="45" customHeight="1" spans="1:12">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="20" t="s">
         <v>44</v>
       </c>
       <c r="B8" s="12" t="s">
@@ -1848,63 +1852,63 @@
       <c r="E8" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="20"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="23"/>
       <c r="I8" s="7" t="s">
         <v>48</v>
       </c>
       <c r="J8" s="46"/>
-      <c r="K8" s="12" t="s">
+      <c r="K8" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="L8" s="12"/>
+      <c r="L8" s="13"/>
     </row>
     <row r="9" ht="45" customHeight="1" spans="1:12">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21" t="s">
+      <c r="B9" s="24"/>
+      <c r="C9" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="21"/>
-      <c r="E9" s="22" t="s">
+      <c r="D9" s="24"/>
+      <c r="E9" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22" t="s">
+      <c r="F9" s="25"/>
+      <c r="G9" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="23"/>
+      <c r="H9" s="26"/>
       <c r="I9" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="21"/>
+      <c r="J9" s="24"/>
       <c r="K9" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="L9" s="22" t="s">
+      <c r="L9" s="49" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1" spans="1:12">
-      <c r="A10" s="24"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="25" t="s">
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
     </row>
     <row r="11" ht="45" customHeight="1" spans="1:12">
       <c r="A11" s="2" t="s">
@@ -1923,25 +1927,25 @@
       <c r="L11" s="2"/>
     </row>
     <row r="12" ht="35.1" customHeight="1" spans="1:12">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="29" t="s">
         <v>1</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="27"/>
-      <c r="F12" s="28" t="s">
+      <c r="E12" s="30"/>
+      <c r="F12" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
       <c r="J12" s="37" t="s">
         <v>6</v>
       </c>
@@ -1958,18 +1962,18 @@
       <c r="C13" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="29"/>
+      <c r="D13" s="32"/>
       <c r="E13" s="11" t="s">
         <v>61</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="50" t="s">
+      <c r="I13" s="50"/>
+      <c r="J13" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="K13" s="51" t="s">
+      <c r="K13" s="52" t="s">
         <v>63</v>
       </c>
       <c r="L13" s="7" t="s">
@@ -1977,33 +1981,33 @@
       </c>
     </row>
     <row r="14" ht="35.1" customHeight="1" spans="1:12">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30" t="s">
+      <c r="B14" s="13"/>
+      <c r="C14" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="30"/>
-      <c r="E14" s="31" t="s">
+      <c r="D14" s="13"/>
+      <c r="E14" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
       <c r="I14" s="33"/>
-      <c r="J14" s="30" t="s">
+      <c r="J14" s="13" t="s">
         <v>67</v>
       </c>
       <c r="K14" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="L14" s="30" t="s">
+      <c r="L14" s="13" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="15" ht="35.1" customHeight="1" spans="1:12">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="16" t="s">
         <v>70</v>
       </c>
       <c r="B15" s="33" t="s">
@@ -2013,46 +2017,46 @@
         <v>72</v>
       </c>
       <c r="D15" s="35"/>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="52" t="s">
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="K15" s="53"/>
-      <c r="L15" s="54" t="s">
+      <c r="K15" s="54"/>
+      <c r="L15" s="55" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="16" ht="51.95" customHeight="1" spans="1:12">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21" t="s">
+      <c r="B16" s="24"/>
+      <c r="C16" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="21"/>
-      <c r="E16" s="22" t="s">
+      <c r="D16" s="24"/>
+      <c r="E16" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22" t="s">
+      <c r="F16" s="25"/>
+      <c r="G16" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="23"/>
+      <c r="H16" s="26"/>
       <c r="I16" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="J16" s="21"/>
+      <c r="J16" s="24"/>
       <c r="K16" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="L16" s="22" t="s">
+      <c r="L16" s="49" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2110,7 +2114,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2 B7:D7 B8:D8 B12"/>
   </dataValidations>
   <pageMargins left="0.776388888888889" right="0.776388888888889" top="0.776388888888889" bottom="0.776388888888889" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="55" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="54" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
@@ -1634,15 +1634,15 @@
   <dimension ref="A1:L29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.625" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.5" style="1" customWidth="1"/>
     <col min="11" max="11" width="9.625" style="1" customWidth="1"/>
     <col min="12" max="12" width="19.25" style="1" customWidth="1"/>
@@ -2114,7 +2114,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2 B7:D7 B8:D8 B12"/>
   </dataValidations>
   <pageMargins left="0.776388888888889" right="0.776388888888889" top="0.776388888888889" bottom="0.776388888888889" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="54" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="47" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23775" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="2.差旅费用报销单" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="75">
   <si>
     <t>差旅费用报销单</t>
   </si>
@@ -201,9 +201,6 @@
   </si>
   <si>
     <t>{expSign}</t>
-  </si>
-  <si>
-    <t>裁切线</t>
   </si>
   <si>
     <t>成本一览表</t>
@@ -660,7 +657,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -758,15 +755,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="dashed">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -926,7 +914,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -938,34 +926,34 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1157,11 +1145,11 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1205,11 +1193,11 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1257,7 +1245,7 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1899,9 +1887,7 @@
       <c r="B10" s="27"/>
       <c r="C10" s="27"/>
       <c r="D10" s="27"/>
-      <c r="E10" s="28" t="s">
-        <v>57</v>
-      </c>
+      <c r="E10" s="28"/>
       <c r="F10" s="28"/>
       <c r="G10" s="28"/>
       <c r="H10" s="28"/>
@@ -1912,7 +1898,7 @@
     </row>
     <row r="11" ht="45" customHeight="1" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1956,25 +1942,25 @@
     </row>
     <row r="13" ht="35.1" customHeight="1" spans="1:12">
       <c r="A13" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D13" s="32"/>
       <c r="E13" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
       <c r="I13" s="50"/>
       <c r="J13" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="52" t="s">
         <v>62</v>
-      </c>
-      <c r="K13" s="52" t="s">
-        <v>63</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>14</v>
@@ -1982,54 +1968,54 @@
     </row>
     <row r="14" ht="35.1" customHeight="1" spans="1:12">
       <c r="A14" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F14" s="14"/>
       <c r="G14" s="14"/>
       <c r="H14" s="14"/>
       <c r="I14" s="33"/>
       <c r="J14" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="K14" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="K14" s="33" t="s">
+      <c r="L14" s="13" t="s">
         <v>68</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="15" ht="35.1" customHeight="1" spans="1:12">
       <c r="A15" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="C15" s="34" t="s">
         <v>71</v>
-      </c>
-      <c r="C15" s="34" t="s">
-        <v>72</v>
       </c>
       <c r="D15" s="35"/>
       <c r="E15" s="18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F15" s="18"/>
       <c r="G15" s="18"/>
       <c r="H15" s="18"/>
       <c r="I15" s="18"/>
       <c r="J15" s="53" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K15" s="54"/>
       <c r="L15" s="55" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" ht="51.95" customHeight="1" spans="1:12">
@@ -2111,7 +2097,7 @@
     <mergeCell ref="L3:L4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2 B7:D7 B8:D8 B12"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2 B12 B7:D8"/>
   </dataValidations>
   <pageMargins left="0.776388888888889" right="0.776388888888889" top="0.776388888888889" bottom="0.776388888888889" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="47" orientation="portrait"/>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
@@ -10,7 +10,7 @@
     <sheet name="2.差旅费用报销单" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'2.差旅费用报销单'!$A$1:$L$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'2.差旅费用报销单'!$A$1:$L$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -191,10 +191,10 @@
     <t>会计：</t>
   </si>
   <si>
-    <t xml:space="preserve"> 出纳：</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 部门负责人：</t>
+    <t>出纳：</t>
+  </si>
+  <si>
+    <t>部门负责人：</t>
   </si>
   <si>
     <t>报销人：</t>
@@ -271,7 +271,7 @@
     <numFmt numFmtId="177" formatCode="0.00_ "/>
     <numFmt numFmtId="178" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="29">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -287,10 +287,36 @@
     </font>
     <font>
       <b/>
-      <sz val="22"/>
+      <sz val="36"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -301,12 +327,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -657,7 +677,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -755,6 +775,30 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -893,31 +937,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -926,338 +958,359 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="31" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="31" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="7" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="7" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="7" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="7" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="7" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="7" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1619,488 +1672,686 @@
     <tabColor rgb="FFFFFF00"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="19.25" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="21.125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.5" style="2" customWidth="1"/>
+    <col min="7" max="7" width="12.75" style="2" customWidth="1"/>
+    <col min="8" max="8" width="14.125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15.375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="15.5" style="2" customWidth="1"/>
+    <col min="12" max="12" width="28.5" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="50.1" customHeight="1" spans="1:12">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="1" customFormat="1" ht="48" customHeight="1" spans="1:12">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" ht="35.1" customHeight="1" spans="1:12">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="48" customHeight="1" spans="1:12">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="6" t="s">
+      <c r="E2" s="7"/>
+      <c r="F2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="37" t="s">
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="38" t="s">
+      <c r="K2" s="43"/>
+      <c r="L2" s="44" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="45" customHeight="1" spans="1:12">
-      <c r="A3" s="7" t="s">
+    <row r="3" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9" t="s">
+      <c r="D3" s="11"/>
+      <c r="E3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="9"/>
-      <c r="G3" s="8" t="s">
+      <c r="F3" s="12"/>
+      <c r="G3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="8"/>
-      <c r="I3" s="39" t="s">
+      <c r="H3" s="11"/>
+      <c r="I3" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="9"/>
-      <c r="K3" s="40" t="s">
+      <c r="J3" s="12"/>
+      <c r="K3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="40" t="s">
+      <c r="L3" s="46" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1" spans="1:12">
-      <c r="A4" s="7" t="s">
+    <row r="4" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-    </row>
-    <row r="5" ht="45" customHeight="1" spans="1:12">
-      <c r="A5" s="12" t="s">
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="41" t="s">
+      <c r="L5" s="15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1" spans="1:12">
-      <c r="A6" s="16" t="s">
+    <row r="6" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A8" s="15"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A9" s="15"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A11" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B11" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="42" t="s">
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="43"/>
-      <c r="K6" s="44" t="s">
+      <c r="J11" s="47"/>
+      <c r="K11" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="L6" s="45"/>
-    </row>
-    <row r="7" ht="45" customHeight="1" spans="1:12">
-      <c r="A7" s="20" t="s">
+      <c r="L11" s="49"/>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A12" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B12" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="7" t="s">
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F12" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="22"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="7" t="s">
+      <c r="G12" s="16"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="46"/>
-      <c r="K7" s="12" t="s">
+      <c r="J12" s="21"/>
+      <c r="K12" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="12"/>
-    </row>
-    <row r="8" ht="45" customHeight="1" spans="1:12">
-      <c r="A8" s="20" t="s">
+      <c r="L12" s="15"/>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A13" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B13" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="7" t="s">
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F13" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="22"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="7" t="s">
+      <c r="G13" s="16"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="46"/>
-      <c r="K8" s="13" t="s">
+      <c r="J13" s="21"/>
+      <c r="K13" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="L8" s="13"/>
-    </row>
-    <row r="9" ht="45" customHeight="1" spans="1:12">
-      <c r="A9" s="24" t="s">
+      <c r="L13" s="15"/>
+    </row>
+    <row r="14" ht="52" customHeight="1" spans="1:12">
+      <c r="A14" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="24"/>
-      <c r="C9" s="24" t="s">
+      <c r="B14" s="23"/>
+      <c r="C14" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="25" t="s">
+      <c r="D14" s="23"/>
+      <c r="E14" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25" t="s">
+      <c r="F14" s="24"/>
+      <c r="G14" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="26"/>
-      <c r="I9" s="47" t="s">
+      <c r="H14" s="23"/>
+      <c r="I14" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="24"/>
-      <c r="K9" s="48" t="s">
+      <c r="J14" s="23"/>
+      <c r="K14" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="L9" s="49" t="s">
+      <c r="L14" s="24" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1" spans="1:12">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="27"/>
-      <c r="L10" s="27"/>
-    </row>
-    <row r="11" ht="45" customHeight="1" spans="1:12">
-      <c r="A11" s="2" t="s">
+    <row r="15" ht="45" customHeight="1" spans="1:12">
+      <c r="A15" s="25"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+    </row>
+    <row r="16" customFormat="1" ht="45" customHeight="1" spans="1:12">
+      <c r="A16" s="27"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+    </row>
+    <row r="17" customFormat="1" ht="45" customHeight="1" spans="1:12">
+      <c r="A17" s="27"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="27"/>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="48" customHeight="1" spans="1:12">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="48" customHeight="1" spans="1:12">
+      <c r="A19" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-    </row>
-    <row r="12" ht="35.1" customHeight="1" spans="1:12">
-      <c r="A12" s="29" t="s">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="48" customHeight="1" spans="1:12">
+      <c r="A20" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C20" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D20" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="30"/>
-      <c r="F12" s="31" t="s">
+      <c r="E20" s="31"/>
+      <c r="F20" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="37" t="s">
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="K12" s="37"/>
-      <c r="L12" s="38" t="s">
+      <c r="K20" s="52"/>
+      <c r="L20" s="44" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" ht="35.1" customHeight="1" spans="1:12">
-      <c r="A13" s="7" t="s">
+    <row r="21" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A21" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="11" t="s">
+      <c r="B21" s="10"/>
+      <c r="C21" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="32"/>
-      <c r="E13" s="11" t="s">
+      <c r="D21" s="34"/>
+      <c r="E21" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="51" t="s">
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="K13" s="52" t="s">
+      <c r="K21" s="55" t="s">
         <v>62</v>
       </c>
-      <c r="L13" s="7" t="s">
+      <c r="L21" s="10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" ht="35.1" customHeight="1" spans="1:12">
-      <c r="A14" s="13" t="s">
+    <row r="22" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A22" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13" t="s">
+      <c r="B22" s="15"/>
+      <c r="C22" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="15" t="s">
+      <c r="D22" s="15"/>
+      <c r="E22" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="13" t="s">
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="K14" s="33" t="s">
+      <c r="K22" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="L14" s="13" t="s">
+      <c r="L22" s="15" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="15" ht="35.1" customHeight="1" spans="1:12">
-      <c r="A15" s="16" t="s">
+    <row r="23" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="15"/>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A24" s="15"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="15"/>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A25" s="15"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="15"/>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A26" s="15"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="15"/>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A27" s="15"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="15"/>
+    </row>
+    <row r="28" ht="35.1" customHeight="1" spans="1:12">
+      <c r="A28" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B28" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C28" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="35"/>
-      <c r="E15" s="18" t="s">
+      <c r="D28" s="40"/>
+      <c r="E28" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="53" t="s">
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="K15" s="54"/>
-      <c r="L15" s="55" t="s">
+      <c r="K28" s="57"/>
+      <c r="L28" s="58" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" ht="51.95" customHeight="1" spans="1:12">
-      <c r="A16" s="24" t="s">
+    <row r="29" ht="51.95" customHeight="1" spans="1:12">
+      <c r="A29" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24" t="s">
+      <c r="B29" s="23"/>
+      <c r="C29" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="24"/>
-      <c r="E16" s="25" t="s">
+      <c r="D29" s="23"/>
+      <c r="E29" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25" t="s">
+      <c r="F29" s="24"/>
+      <c r="G29" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="26"/>
-      <c r="I16" s="47" t="s">
+      <c r="H29" s="23"/>
+      <c r="I29" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="J16" s="24"/>
-      <c r="K16" s="48" t="s">
+      <c r="J29" s="23"/>
+      <c r="K29" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="L16" s="49" t="s">
+      <c r="L29" s="24" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17" ht="54.95" customHeight="1"/>
-    <row r="18" ht="35.1" customHeight="1"/>
-    <row r="19" ht="45" customHeight="1"/>
-    <row r="20" ht="45" customHeight="1"/>
-    <row r="21" ht="45" customHeight="1"/>
-    <row r="22" ht="45" customHeight="1"/>
-    <row r="23" ht="45" customHeight="1"/>
-    <row r="24" ht="45" customHeight="1"/>
-    <row r="25" ht="45" customHeight="1"/>
-    <row r="26" ht="45" customHeight="1"/>
-    <row r="27" ht="45" customHeight="1"/>
-    <row r="28" ht="35.1" customHeight="1"/>
-    <row r="29" ht="35.1" customHeight="1"/>
+    <row r="30" ht="54.95" customHeight="1"/>
+    <row r="31" ht="35.1" customHeight="1"/>
+    <row r="32" ht="45" customHeight="1"/>
+    <row r="33" ht="45" customHeight="1"/>
+    <row r="34" ht="45" customHeight="1"/>
+    <row r="35" ht="45" customHeight="1"/>
+    <row r="36" ht="45" customHeight="1"/>
+    <row r="37" ht="45" customHeight="1"/>
+    <row r="38" ht="45" customHeight="1"/>
+    <row r="39" ht="45" customHeight="1"/>
+    <row r="40" ht="45" customHeight="1"/>
+    <row r="41" ht="35.1" customHeight="1"/>
+    <row r="42" ht="35.1" customHeight="1"/>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="50">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:I2"/>
+    <mergeCell ref="J2:K2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="I3:J3"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:I13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:I14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:I15"/>
-    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="A19:L19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:I21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:I22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:I23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:I24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:I25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:I26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:I27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:I28"/>
+    <mergeCell ref="J28:K28"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="L3:L4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2 B12 B7:D8"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2 B20 B12:D13"/>
   </dataValidations>
-  <pageMargins left="0.776388888888889" right="0.776388888888889" top="0.776388888888889" bottom="0.776388888888889" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="47" orientation="portrait"/>
+  <pageMargins left="0.472222222222222" right="0.354166666666667" top="0.196527777777778" bottom="0.776388888888889" header="0.236111111111111" footer="0.3"/>
+  <pageSetup paperSize="9" scale="42" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
@@ -320,13 +320,13 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1082,7 +1082,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1104,19 +1104,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="31" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1177,6 +1173,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1200,19 +1200,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="31" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="31" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1279,14 +1275,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1675,7 +1663,7 @@
   <dimension ref="A1:L42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16.625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="19.75" style="2" customWidth="1"/>
     <col min="2" max="2" width="21.125" style="2" customWidth="1"/>
     <col min="3" max="3" width="15.875" style="2" customWidth="1"/>
     <col min="4" max="4" width="13.25" style="2" customWidth="1"/>
@@ -1686,7 +1674,7 @@
     <col min="9" max="9" width="15.375" style="2" customWidth="1"/>
     <col min="10" max="10" width="15.125" style="2" customWidth="1"/>
     <col min="11" max="11" width="15.5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="28.5" style="2" customWidth="1"/>
+    <col min="12" max="12" width="33.625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="48" customHeight="1" spans="1:12">
@@ -1712,276 +1700,276 @@
       <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="42" t="s">
+      <c r="I2" s="8"/>
+      <c r="J2" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="43"/>
-      <c r="L2" s="44" t="s">
+      <c r="K2" s="42"/>
+      <c r="L2" s="43" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="9"/>
+      <c r="C3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="12" t="s">
+      <c r="D3" s="10"/>
+      <c r="E3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="11"/>
+      <c r="G3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="45" t="s">
+      <c r="H3" s="10"/>
+      <c r="I3" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="12"/>
-      <c r="K3" s="46" t="s">
+      <c r="J3" s="11"/>
+      <c r="K3" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="46" t="s">
+      <c r="L3" s="45" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="47" t="s">
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="47"/>
-      <c r="K11" s="48" t="s">
+      <c r="J11" s="46"/>
+      <c r="K11" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="L11" s="49"/>
+      <c r="L11" s="48"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="10" t="s">
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="16"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="10" t="s">
+      <c r="G12" s="15"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="J12" s="21"/>
-      <c r="K12" s="15" t="s">
+      <c r="J12" s="20"/>
+      <c r="K12" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="L12" s="15"/>
+      <c r="L12" s="14"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="10" t="s">
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="17" t="s">
+      <c r="F13" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="16"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="10" t="s">
+      <c r="G13" s="15"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="J13" s="21"/>
-      <c r="K13" s="15" t="s">
+      <c r="J13" s="20"/>
+      <c r="K13" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="L13" s="15"/>
+      <c r="L13" s="14"/>
     </row>
     <row r="14" ht="52" customHeight="1" spans="1:12">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="23"/>
+      <c r="B14" s="22"/>
       <c r="C14" s="23" t="s">
         <v>51</v>
       </c>
@@ -1993,12 +1981,12 @@
       <c r="G14" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H14" s="23"/>
-      <c r="I14" s="50" t="s">
+      <c r="H14" s="22"/>
+      <c r="I14" s="23" t="s">
         <v>54</v>
       </c>
       <c r="J14" s="23"/>
-      <c r="K14" s="51" t="s">
+      <c r="K14" s="49" t="s">
         <v>55</v>
       </c>
       <c r="L14" s="24" t="s">
@@ -2081,183 +2069,183 @@
       <c r="A20" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="30"/>
+      <c r="D20" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="E20" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="31"/>
-      <c r="F20" s="32" t="s">
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="52" t="s">
+      <c r="I20" s="32"/>
+      <c r="J20" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="K20" s="52"/>
-      <c r="L20" s="44" t="s">
+      <c r="K20" s="42"/>
+      <c r="L20" s="43" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="14" t="s">
+      <c r="B21" s="9"/>
+      <c r="C21" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="34"/>
-      <c r="E21" s="14" t="s">
+      <c r="D21" s="33"/>
+      <c r="E21" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="54" t="s">
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="K21" s="55" t="s">
+      <c r="K21" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="L21" s="10" t="s">
+      <c r="L21" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15" t="s">
+      <c r="B22" s="14"/>
+      <c r="C22" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="D22" s="15"/>
-      <c r="E22" s="17" t="s">
+      <c r="D22" s="14"/>
+      <c r="E22" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="15" t="s">
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="K22" s="22" t="s">
+      <c r="K22" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="L22" s="15" t="s">
+      <c r="L22" s="14" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="15"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="14"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A24" s="15"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="15"/>
+      <c r="A24" s="14"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="34"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="14"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A25" s="15"/>
-      <c r="B25" s="35"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="15"/>
+      <c r="A25" s="14"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="14"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A26" s="15"/>
-      <c r="B26" s="35"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="15"/>
+      <c r="A26" s="14"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="14"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A27" s="15"/>
-      <c r="B27" s="35"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="36"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="15"/>
-    </row>
-    <row r="28" ht="35.1" customHeight="1" spans="1:12">
-      <c r="A28" s="37" t="s">
+      <c r="A27" s="14"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="14"/>
+    </row>
+    <row r="28" ht="69" customHeight="1" spans="1:12">
+      <c r="A28" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="D28" s="40"/>
-      <c r="E28" s="41" t="s">
+      <c r="D28" s="39"/>
+      <c r="E28" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="56" t="s">
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="K28" s="57"/>
-      <c r="L28" s="58" t="s">
+      <c r="K28" s="54"/>
+      <c r="L28" s="55" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="29" ht="51.95" customHeight="1" spans="1:12">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="B29" s="23"/>
+      <c r="B29" s="22"/>
       <c r="C29" s="23" t="s">
         <v>51</v>
       </c>
@@ -2269,12 +2257,12 @@
       <c r="G29" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H29" s="23"/>
-      <c r="I29" s="50" t="s">
+      <c r="H29" s="22"/>
+      <c r="I29" s="23" t="s">
         <v>54</v>
       </c>
       <c r="J29" s="23"/>
-      <c r="K29" s="51" t="s">
+      <c r="K29" s="49" t="s">
         <v>55</v>
       </c>
       <c r="L29" s="24" t="s">
@@ -2295,10 +2283,11 @@
     <row r="41" ht="35.1" customHeight="1"/>
     <row r="42" ht="35.1" customHeight="1"/>
   </sheetData>
-  <mergeCells count="50">
+  <mergeCells count="56">
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C3:D3"/>
@@ -2316,9 +2305,12 @@
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="K13:L13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="I14:J14"/>
     <mergeCell ref="A19:L19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="H20:I20"/>
     <mergeCell ref="J20:K20"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="C21:D21"/>
@@ -2344,6 +2336,8 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:I28"/>
     <mergeCell ref="J28:K28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="I29:J29"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="L3:L4"/>
   </mergeCells>
@@ -2351,7 +2345,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2 B20 B12:D13"/>
   </dataValidations>
   <pageMargins left="0.472222222222222" right="0.354166666666667" top="0.196527777777778" bottom="0.776388888888889" header="0.236111111111111" footer="0.3"/>
-  <pageSetup paperSize="9" scale="42" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="41" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
@@ -1101,7 +1101,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1109,7 +1109,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="31" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1201,7 +1201,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1251,7 +1251,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1665,8 +1665,8 @@
   <cols>
     <col min="1" max="1" width="19.75" style="2" customWidth="1"/>
     <col min="2" max="2" width="21.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.25" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.625" style="2" customWidth="1"/>
     <col min="5" max="5" width="15.375" style="2" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="2" customWidth="1"/>
     <col min="7" max="7" width="12.75" style="2" customWidth="1"/>
@@ -2345,7 +2345,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2 B20 B12:D13"/>
   </dataValidations>
   <pageMargins left="0.472222222222222" right="0.354166666666667" top="0.196527777777778" bottom="0.776388888888889" header="0.236111111111111" footer="0.3"/>
-  <pageSetup paperSize="9" scale="41" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="38" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
@@ -2035,7 +2035,7 @@
       <c r="K17" s="27"/>
       <c r="L17" s="27"/>
     </row>
-    <row r="18" s="1" customFormat="1" ht="48" customHeight="1" spans="1:12">
+    <row r="18" s="1" customFormat="1" ht="240" customHeight="1" spans="1:12">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="71">
   <si>
     <t>差旅费用报销单</t>
   </si>
@@ -182,19 +182,7 @@
     <t>{devSubject}</t>
   </si>
   <si>
-    <t>总经理：</t>
-  </si>
-  <si>
-    <t>财务负责人：</t>
-  </si>
-  <si>
-    <t>会计：</t>
-  </si>
-  <si>
-    <t>出纳：</t>
-  </si>
-  <si>
-    <t>部门负责人：</t>
+    <t>总经理：       财务负责人：       会计：       出纳：       部门负责人：       分管领导：</t>
   </si>
   <si>
     <t>报销人：</t>
@@ -1082,7 +1070,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1169,15 +1157,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1276,6 +1256,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1713,11 +1697,11 @@
         <v>5</v>
       </c>
       <c r="I2" s="8"/>
-      <c r="J2" s="41" t="s">
+      <c r="J2" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="42"/>
-      <c r="L2" s="43" t="s">
+      <c r="K2" s="40"/>
+      <c r="L2" s="41" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1738,14 +1722,14 @@
         <v>11</v>
       </c>
       <c r="H3" s="10"/>
-      <c r="I3" s="44" t="s">
+      <c r="I3" s="42" t="s">
         <v>12</v>
       </c>
       <c r="J3" s="11"/>
-      <c r="K3" s="45" t="s">
+      <c r="K3" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="45" t="s">
+      <c r="L3" s="43" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1904,14 +1888,14 @@
       <c r="F11" s="18"/>
       <c r="G11" s="18"/>
       <c r="H11" s="19"/>
-      <c r="I11" s="46" t="s">
+      <c r="I11" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="46"/>
-      <c r="K11" s="47" t="s">
+      <c r="J11" s="44"/>
+      <c r="K11" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="L11" s="48"/>
+      <c r="L11" s="46"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
       <c r="A12" s="20" t="s">
@@ -1970,70 +1954,62 @@
         <v>50</v>
       </c>
       <c r="B14" s="22"/>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="23"/>
-      <c r="E14" s="24" t="s">
+      <c r="L14" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="H14" s="22"/>
-      <c r="I14" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="J14" s="23"/>
-      <c r="K14" s="49" t="s">
-        <v>55</v>
-      </c>
-      <c r="L14" s="24" t="s">
-        <v>56</v>
-      </c>
     </row>
     <row r="15" ht="45" customHeight="1" spans="1:12">
-      <c r="A15" s="25"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
     </row>
     <row r="16" customFormat="1" ht="45" customHeight="1" spans="1:12">
-      <c r="A16" s="27"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
-      <c r="L16" s="27"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
     </row>
     <row r="17" customFormat="1" ht="45" customHeight="1" spans="1:12">
-      <c r="A17" s="27"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="27"/>
-      <c r="L17" s="27"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
     </row>
     <row r="18" s="1" customFormat="1" ht="240" customHeight="1" spans="1:12">
       <c r="A18" s="3"/>
@@ -2051,7 +2027,7 @@
     </row>
     <row r="19" s="1" customFormat="1" ht="48" customHeight="1" spans="1:12">
       <c r="A19" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -2066,54 +2042,54 @@
       <c r="L19" s="3"/>
     </row>
     <row r="20" s="1" customFormat="1" ht="48" customHeight="1" spans="1:12">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="30"/>
-      <c r="D20" s="31" t="s">
+      <c r="C20" s="28"/>
+      <c r="D20" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="30" t="s">
+      <c r="E20" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="32" t="s">
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="I20" s="32"/>
-      <c r="J20" s="42" t="s">
+      <c r="I20" s="30"/>
+      <c r="J20" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="K20" s="42"/>
-      <c r="L20" s="43" t="s">
+      <c r="K20" s="40"/>
+      <c r="L20" s="41" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
       <c r="A21" s="9" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" s="33"/>
+        <v>55</v>
+      </c>
+      <c r="D21" s="31"/>
       <c r="E21" s="13" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="12"/>
       <c r="H21" s="12"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="51" t="s">
-        <v>61</v>
-      </c>
-      <c r="K21" s="52" t="s">
-        <v>62</v>
+      <c r="I21" s="49"/>
+      <c r="J21" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="K21" s="51" t="s">
+        <v>58</v>
       </c>
       <c r="L21" s="9" t="s">
         <v>14</v>
@@ -2121,28 +2097,28 @@
     </row>
     <row r="22" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
       <c r="A22" s="14" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="16" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
       <c r="H22" s="15"/>
       <c r="I22" s="21"/>
       <c r="J22" s="14" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K22" s="21" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="L22" s="14" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
@@ -2161,84 +2137,84 @@
     </row>
     <row r="24" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
       <c r="A24" s="14"/>
-      <c r="B24" s="34"/>
+      <c r="B24" s="32"/>
       <c r="C24" s="14"/>
-      <c r="D24" s="34"/>
+      <c r="D24" s="32"/>
       <c r="E24" s="16"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="34"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="32"/>
       <c r="J24" s="14"/>
       <c r="K24" s="21"/>
       <c r="L24" s="14"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
       <c r="A25" s="14"/>
-      <c r="B25" s="34"/>
+      <c r="B25" s="32"/>
       <c r="C25" s="14"/>
-      <c r="D25" s="34"/>
+      <c r="D25" s="32"/>
       <c r="E25" s="16"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="34"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="32"/>
       <c r="J25" s="14"/>
       <c r="K25" s="21"/>
       <c r="L25" s="14"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
       <c r="A26" s="14"/>
-      <c r="B26" s="34"/>
+      <c r="B26" s="32"/>
       <c r="C26" s="14"/>
-      <c r="D26" s="34"/>
+      <c r="D26" s="32"/>
       <c r="E26" s="16"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="34"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="32"/>
       <c r="J26" s="14"/>
       <c r="K26" s="21"/>
       <c r="L26" s="14"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
       <c r="A27" s="14"/>
-      <c r="B27" s="34"/>
+      <c r="B27" s="32"/>
       <c r="C27" s="14"/>
-      <c r="D27" s="34"/>
+      <c r="D27" s="32"/>
       <c r="E27" s="16"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="34"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="32"/>
       <c r="J27" s="14"/>
       <c r="K27" s="21"/>
       <c r="L27" s="14"/>
     </row>
     <row r="28" ht="69" customHeight="1" spans="1:12">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="37"/>
+      <c r="E28" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="B28" s="37" t="s">
+      <c r="K28" s="53"/>
+      <c r="L28" s="54" t="s">
         <v>70</v>
-      </c>
-      <c r="C28" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="D28" s="39"/>
-      <c r="E28" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="53" t="s">
-        <v>73</v>
-      </c>
-      <c r="K28" s="54"/>
-      <c r="L28" s="55" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="29" ht="51.95" customHeight="1" spans="1:12">
@@ -2246,27 +2222,19 @@
         <v>50</v>
       </c>
       <c r="B29" s="22"/>
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="D29" s="23"/>
-      <c r="E29" s="24" t="s">
+      <c r="L29" s="48" t="s">
         <v>52</v>
-      </c>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="H29" s="22"/>
-      <c r="I29" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="J29" s="23"/>
-      <c r="K29" s="49" t="s">
-        <v>55</v>
-      </c>
-      <c r="L29" s="24" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="30" ht="54.95" customHeight="1"/>
@@ -2283,7 +2251,7 @@
     <row r="41" ht="35.1" customHeight="1"/>
     <row r="42" ht="35.1" customHeight="1"/>
   </sheetData>
-  <mergeCells count="56">
+  <mergeCells count="54">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:G2"/>
@@ -2305,8 +2273,7 @@
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="K13:L13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A14:J14"/>
     <mergeCell ref="A19:L19"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="E20:G20"/>
@@ -2336,8 +2303,7 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:I28"/>
     <mergeCell ref="J28:K28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="A29:J29"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="L3:L4"/>
   </mergeCells>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
@@ -182,7 +182,7 @@
     <t>{devSubject}</t>
   </si>
   <si>
-    <t>总经理：       财务负责人：       会计：       出纳：       部门负责人：       分管领导：</t>
+    <t>总经理：       财务负责人：       会计：       出纳：         分管领导：       部门负责人：</t>
   </si>
   <si>
     <t>报销人：</t>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
@@ -29,8 +29,40 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="E22" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+120字</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="69">
   <si>
     <t>差旅费用报销单</t>
   </si>
@@ -131,9 +163,6 @@
     <t>{data1.subTotal}</t>
   </si>
   <si>
-    <t>事由：{data1.memo}</t>
-  </si>
-  <si>
     <t xml:space="preserve">大写总金额                     </t>
   </si>
   <si>
@@ -182,10 +211,7 @@
     <t>{devSubject}</t>
   </si>
   <si>
-    <t>总经理：       财务负责人：       会计：       出纳：         分管领导：       部门负责人：</t>
-  </si>
-  <si>
-    <t>报销人：</t>
+    <t>审批：         审核：          复核：        出纳：        分管领导：        部门负责人：        报销人：</t>
   </si>
   <si>
     <t>{expSign}</t>
@@ -259,7 +285,7 @@
     <numFmt numFmtId="177" formatCode="0.00_ "/>
     <numFmt numFmtId="178" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -469,6 +495,17 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1070,7 +1107,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1080,7 +1117,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1096,7 +1140,7 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1112,15 +1156,23 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1128,11 +1180,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1144,7 +1200,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1152,7 +1212,7 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1164,7 +1224,7 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1172,7 +1232,7 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1188,7 +1248,15 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="31" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1218,11 +1286,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1234,7 +1302,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1242,7 +1310,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1254,19 +1322,31 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1274,7 +1354,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1647,594 +1731,581 @@
   <dimension ref="A1:L42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="19.75" style="2" customWidth="1"/>
-    <col min="2" max="2" width="21.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="14.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.5" style="2" customWidth="1"/>
-    <col min="7" max="7" width="12.75" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15.125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="15.5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="33.625" style="2" customWidth="1"/>
+    <col min="1" max="4" width="13.625" style="2" customWidth="1"/>
+    <col min="5" max="9" width="20.625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="13.625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="13.625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="23.6666666666667" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="48" customHeight="1" spans="1:12">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="48" customHeight="1" spans="1:12">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="6" t="s">
+      <c r="C2" s="7"/>
+      <c r="D2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="8" t="s">
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="8"/>
-      <c r="J2" s="39" t="s">
+      <c r="I2" s="10"/>
+      <c r="J2" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="40"/>
-      <c r="L2" s="41" t="s">
+      <c r="K2" s="48"/>
+      <c r="L2" s="49" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="12"/>
+      <c r="E3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10" t="s">
+      <c r="F3" s="13"/>
+      <c r="G3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="10"/>
-      <c r="I3" s="42" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="11"/>
-      <c r="K3" s="43" t="s">
+      <c r="J3" s="13"/>
+      <c r="K3" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="43" t="s">
+      <c r="L3" s="51" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="K5" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="L5" s="18"/>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A11" s="11" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A11" s="9" t="s">
+      <c r="B11" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="44" t="s">
+      <c r="J11" s="52"/>
+      <c r="K11" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="44"/>
-      <c r="K11" s="45" t="s">
+      <c r="L11" s="54"/>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A12" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="L11" s="46"/>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A12" s="20" t="s">
+      <c r="B12" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="9" t="s">
+      <c r="F12" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="G12" s="19"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="15"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="9" t="s">
+      <c r="J12" s="55"/>
+      <c r="K12" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="J12" s="20"/>
-      <c r="K12" s="14" t="s">
+      <c r="L12" s="18"/>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
+      <c r="A13" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="L12" s="14"/>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A13" s="20" t="s">
+      <c r="B13" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="9" t="s">
+      <c r="F13" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="G13" s="19"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="9" t="s">
+      <c r="J13" s="55"/>
+      <c r="K13" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="J13" s="20"/>
-      <c r="K13" s="14" t="s">
+      <c r="L13" s="18"/>
+    </row>
+    <row r="14" ht="65" customHeight="1" spans="1:12">
+      <c r="A14" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="L13" s="14"/>
-    </row>
-    <row r="14" ht="52" customHeight="1" spans="1:12">
-      <c r="A14" s="22" t="s">
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="47" t="s">
+    </row>
+    <row r="15" ht="45" customHeight="1" spans="1:12">
+      <c r="A15" s="29"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+    </row>
+    <row r="16" customFormat="1" ht="45" customHeight="1" spans="1:12">
+      <c r="A16" s="31"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+    </row>
+    <row r="17" customFormat="1" ht="45" customHeight="1" spans="1:12">
+      <c r="A17" s="31"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="54" customHeight="1" spans="1:12">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="36" customHeight="1" spans="1:12">
+      <c r="A19" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="L14" s="48" t="s">
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="48" customHeight="1" spans="1:12">
+      <c r="A20" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="34"/>
+      <c r="D20" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="37"/>
+      <c r="J20" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="K20" s="48"/>
+      <c r="L20" s="49" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="69" customHeight="1" spans="1:12">
+      <c r="A21" s="11" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="15" ht="45" customHeight="1" spans="1:12">
-      <c r="A15" s="23"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="23"/>
-    </row>
-    <row r="16" customFormat="1" ht="45" customHeight="1" spans="1:12">
-      <c r="A16" s="25"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-    </row>
-    <row r="17" customFormat="1" ht="45" customHeight="1" spans="1:12">
-      <c r="A17" s="25"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="240" customHeight="1" spans="1:12">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="48" customHeight="1" spans="1:12">
-      <c r="A19" s="3" t="s">
+      <c r="B21" s="11"/>
+      <c r="C21" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-    </row>
-    <row r="20" s="1" customFormat="1" ht="48" customHeight="1" spans="1:12">
-      <c r="A20" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="B20" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" s="30"/>
-      <c r="J20" s="40" t="s">
-        <v>6</v>
-      </c>
-      <c r="K20" s="40"/>
-      <c r="L20" s="41" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A21" s="9" t="s">
+      <c r="D21" s="39"/>
+      <c r="E21" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="13" t="s">
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="31"/>
-      <c r="E21" s="13" t="s">
+      <c r="K21" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="50" t="s">
+      <c r="L21" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="132" customHeight="1" spans="1:12">
+      <c r="A22" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="K21" s="51" t="s">
+      <c r="B22" s="18"/>
+      <c r="C22" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="L21" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A22" s="14" t="s">
+      <c r="D22" s="18"/>
+      <c r="E22" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14" t="s">
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="16" t="s">
+      <c r="K22" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="14" t="s">
+      <c r="L22" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="K22" s="21" t="s">
+    </row>
+    <row r="23" s="1" customFormat="1" ht="132" customHeight="1" spans="1:12">
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="63"/>
+      <c r="L23" s="18"/>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="132" customHeight="1" spans="1:12">
+      <c r="A24" s="18"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="63"/>
+      <c r="L24" s="18"/>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="132" customHeight="1" spans="1:12">
+      <c r="A25" s="18"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="63"/>
+      <c r="L25" s="18"/>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="132" customHeight="1" spans="1:12">
+      <c r="A26" s="18"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="63"/>
+      <c r="L26" s="18"/>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="132" customHeight="1" spans="1:12">
+      <c r="A27" s="18"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="63"/>
+      <c r="L27" s="18"/>
+    </row>
+    <row r="28" ht="69" customHeight="1" spans="1:12">
+      <c r="A28" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="L22" s="14" t="s">
+      <c r="B28" s="43" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="14"/>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A24" s="14"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="14"/>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A25" s="14"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="14"/>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A26" s="14"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="14"/>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
-      <c r="A27" s="14"/>
-      <c r="B27" s="32"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="21"/>
-      <c r="L27" s="14"/>
-    </row>
-    <row r="28" ht="69" customHeight="1" spans="1:12">
-      <c r="A28" s="34" t="s">
+      <c r="C28" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="35" t="s">
+      <c r="D28" s="45"/>
+      <c r="E28" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="C28" s="36" t="s">
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="D28" s="37"/>
-      <c r="E28" s="38" t="s">
+      <c r="K28" s="65"/>
+      <c r="L28" s="66" t="s">
         <v>68</v>
       </c>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="38"/>
-      <c r="J28" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="K28" s="53"/>
-      <c r="L28" s="54" t="s">
-        <v>70</v>
-      </c>
     </row>
     <row r="29" ht="51.95" customHeight="1" spans="1:12">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="56" t="s">
         <v>50</v>
-      </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="L29" s="48" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="30" ht="54.95" customHeight="1"/>
@@ -2273,7 +2344,7 @@
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="K13:L13"/>
-    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A14:K14"/>
     <mergeCell ref="A19:L19"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="E20:G20"/>
@@ -2303,16 +2374,17 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:I28"/>
     <mergeCell ref="J28:K28"/>
-    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A29:K29"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="L3:L4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2 B20 B12:D13"/>
   </dataValidations>
-  <pageMargins left="0.472222222222222" right="0.354166666666667" top="0.196527777777778" bottom="0.776388888888889" header="0.236111111111111" footer="0.3"/>
-  <pageSetup paperSize="9" scale="38" orientation="portrait"/>
+  <pageMargins left="0.472222222222222" right="0.354166666666667" top="0.196527777777778" bottom="0.236111111111111" header="0.236111111111111" footer="0.3"/>
+  <pageSetup paperSize="9" scale="40" orientation="portrait"/>
   <headerFooter/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
@@ -220,7 +220,7 @@
     <t>成本一览表</t>
   </si>
   <si>
-    <t>项目/合同名称</t>
+    <t>编号与合同名称</t>
   </si>
   <si>
     <t>明细科目</t>
@@ -235,7 +235,7 @@
     <t>进项税额</t>
   </si>
   <si>
-    <t>{data2.prjName}</t>
+    <t>{data2.prjNameNo}</t>
   </si>
   <si>
     <t>{data2.item}</t>
@@ -1107,7 +1107,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1132,12 +1132,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1237,18 +1237,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1455,6 +1443,37 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="635" y="40005"/>
+          <a:ext cx="1997710" cy="588010"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>635</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>40005</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1997710" cy="588010"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="635" y="15661005"/>
           <a:ext cx="1997710" cy="588010"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1731,10 +1750,12 @@
   <dimension ref="A1:L42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="13.625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="19.8166666666667" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.0333333333333" style="2" customWidth="1"/>
+    <col min="3" max="4" width="13.625" style="2" customWidth="1"/>
     <col min="5" max="9" width="20.625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="13.625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="13.625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.25" style="3" customWidth="1"/>
+    <col min="11" max="11" width="15.5" style="2" customWidth="1"/>
     <col min="12" max="12" width="23.6666666666667" style="2" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1762,23 +1783,23 @@
         <v>2</v>
       </c>
       <c r="C2" s="7"/>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7"/>
+      <c r="E2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="10" t="s">
         <v>5</v>
       </c>
       <c r="I2" s="10"/>
-      <c r="J2" s="47" t="s">
+      <c r="J2" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="48"/>
-      <c r="L2" s="49" t="s">
+      <c r="K2" s="45"/>
+      <c r="L2" s="46" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1786,8 +1807,8 @@
       <c r="A3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="12"/>
+      <c r="C3" s="12" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="12"/>
@@ -1799,14 +1820,14 @@
         <v>11</v>
       </c>
       <c r="H3" s="14"/>
-      <c r="I3" s="50" t="s">
+      <c r="I3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="J3" s="13"/>
-      <c r="K3" s="51" t="s">
+      <c r="K3" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="51" t="s">
+      <c r="L3" s="48" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1963,14 +1984,14 @@
       <c r="F11" s="24"/>
       <c r="G11" s="24"/>
       <c r="H11" s="25"/>
-      <c r="I11" s="52" t="s">
+      <c r="I11" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="J11" s="52"/>
-      <c r="K11" s="53" t="s">
+      <c r="J11" s="49"/>
+      <c r="K11" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="L11" s="54"/>
+      <c r="L11" s="51"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="80" customHeight="1" spans="1:12">
       <c r="A12" s="26" t="s">
@@ -1992,7 +2013,7 @@
       <c r="I12" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="J12" s="55"/>
+      <c r="J12" s="52"/>
       <c r="K12" s="18" t="s">
         <v>42</v>
       </c>
@@ -2018,7 +2039,7 @@
       <c r="I13" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="J13" s="55"/>
+      <c r="J13" s="52"/>
       <c r="K13" s="18" t="s">
         <v>48</v>
       </c>
@@ -2038,7 +2059,7 @@
       <c r="I14" s="28"/>
       <c r="J14" s="28"/>
       <c r="K14" s="28"/>
-      <c r="L14" s="56" t="s">
+      <c r="L14" s="53" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2051,8 +2072,8 @@
       <c r="F15" s="30"/>
       <c r="G15" s="30"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="57"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="54"/>
       <c r="K15" s="29"/>
       <c r="L15" s="29"/>
     </row>
@@ -2065,8 +2086,8 @@
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
       <c r="H16" s="32"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="58"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="55"/>
       <c r="K16" s="31"/>
       <c r="L16" s="31"/>
     </row>
@@ -2079,8 +2100,8 @@
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="58"/>
+      <c r="I17" s="55"/>
+      <c r="J17" s="55"/>
       <c r="K17" s="31"/>
       <c r="L17" s="31"/>
     </row>
@@ -2118,27 +2139,27 @@
       <c r="A20" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="34" t="s">
+      <c r="B20" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="35" t="s">
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="36" t="s">
+      <c r="F20" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="37" t="s">
+      <c r="G20" s="9"/>
+      <c r="H20" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="I20" s="37"/>
-      <c r="J20" s="59" t="s">
+      <c r="I20" s="34"/>
+      <c r="J20" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="K20" s="48"/>
-      <c r="L20" s="49" t="s">
+      <c r="K20" s="45"/>
+      <c r="L20" s="46" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2147,21 +2168,21 @@
         <v>52</v>
       </c>
       <c r="B21" s="11"/>
-      <c r="C21" s="38" t="s">
+      <c r="C21" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="D21" s="39"/>
+      <c r="D21" s="36"/>
       <c r="E21" s="16" t="s">
         <v>54</v>
       </c>
       <c r="F21" s="15"/>
       <c r="G21" s="15"/>
       <c r="H21" s="15"/>
-      <c r="I21" s="60"/>
-      <c r="J21" s="61" t="s">
+      <c r="I21" s="57"/>
+      <c r="J21" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="K21" s="62" t="s">
+      <c r="K21" s="59" t="s">
         <v>56</v>
       </c>
       <c r="L21" s="11" t="s">
@@ -2187,7 +2208,7 @@
       <c r="J22" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="K22" s="63" t="s">
+      <c r="K22" s="60" t="s">
         <v>61</v>
       </c>
       <c r="L22" s="18" t="s">
@@ -2205,88 +2226,88 @@
       <c r="H23" s="19"/>
       <c r="I23" s="27"/>
       <c r="J23" s="21"/>
-      <c r="K23" s="63"/>
+      <c r="K23" s="60"/>
       <c r="L23" s="18"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="132" customHeight="1" spans="1:12">
       <c r="A24" s="18"/>
-      <c r="B24" s="40"/>
+      <c r="B24" s="37"/>
       <c r="C24" s="18"/>
-      <c r="D24" s="40"/>
+      <c r="D24" s="37"/>
       <c r="E24" s="20"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="40"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="37"/>
       <c r="J24" s="21"/>
-      <c r="K24" s="63"/>
+      <c r="K24" s="60"/>
       <c r="L24" s="18"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="132" customHeight="1" spans="1:12">
       <c r="A25" s="18"/>
-      <c r="B25" s="40"/>
+      <c r="B25" s="37"/>
       <c r="C25" s="18"/>
-      <c r="D25" s="40"/>
+      <c r="D25" s="37"/>
       <c r="E25" s="20"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="40"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="37"/>
       <c r="J25" s="21"/>
-      <c r="K25" s="63"/>
+      <c r="K25" s="60"/>
       <c r="L25" s="18"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="132" customHeight="1" spans="1:12">
       <c r="A26" s="18"/>
-      <c r="B26" s="40"/>
+      <c r="B26" s="37"/>
       <c r="C26" s="18"/>
-      <c r="D26" s="40"/>
+      <c r="D26" s="37"/>
       <c r="E26" s="20"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="40"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="37"/>
       <c r="J26" s="21"/>
-      <c r="K26" s="63"/>
+      <c r="K26" s="60"/>
       <c r="L26" s="18"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="132" customHeight="1" spans="1:12">
       <c r="A27" s="18"/>
-      <c r="B27" s="40"/>
+      <c r="B27" s="37"/>
       <c r="C27" s="18"/>
-      <c r="D27" s="40"/>
+      <c r="D27" s="37"/>
       <c r="E27" s="20"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="40"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="37"/>
       <c r="J27" s="21"/>
-      <c r="K27" s="63"/>
+      <c r="K27" s="60"/>
       <c r="L27" s="18"/>
     </row>
     <row r="28" ht="69" customHeight="1" spans="1:12">
-      <c r="A28" s="42" t="s">
+      <c r="A28" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="43" t="s">
+      <c r="B28" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="44" t="s">
+      <c r="C28" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="45"/>
-      <c r="E28" s="46" t="s">
+      <c r="D28" s="42"/>
+      <c r="E28" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="F28" s="46"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="46"/>
-      <c r="J28" s="64" t="s">
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="K28" s="65"/>
-      <c r="L28" s="66" t="s">
+      <c r="K28" s="62"/>
+      <c r="L28" s="63" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2304,7 +2325,7 @@
       <c r="I29" s="28"/>
       <c r="J29" s="28"/>
       <c r="K29" s="28"/>
-      <c r="L29" s="56" t="s">
+      <c r="L29" s="53" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2324,8 +2345,8 @@
   </sheetData>
   <mergeCells count="54">
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="A3:B3"/>
@@ -2346,8 +2367,8 @@
     <mergeCell ref="K13:L13"/>
     <mergeCell ref="A14:K14"/>
     <mergeCell ref="A19:L19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="F20:G20"/>
     <mergeCell ref="H20:I20"/>
     <mergeCell ref="J20:K20"/>
     <mergeCell ref="A21:B21"/>
@@ -2379,10 +2400,10 @@
     <mergeCell ref="L3:L4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2 B20 B12:D13"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2 C20 B12:D13"/>
   </dataValidations>
   <pageMargins left="0.472222222222222" right="0.354166666666667" top="0.196527777777778" bottom="0.236111111111111" header="0.236111111111111" footer="0.3"/>
-  <pageSetup paperSize="9" scale="40" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="37" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
@@ -211,10 +211,10 @@
     <t>{devSubject}</t>
   </si>
   <si>
-    <t>审批：         审核：          复核：        出纳：        分管领导：        部门负责人：        报销人：</t>
-  </si>
-  <si>
-    <t>{expSign}</t>
+    <t xml:space="preserve">审批：           审核：            复核：           出纳：           分管领导：            部门负责人：          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 报销人：{expSign}</t>
   </si>
   <si>
     <t>成本一览表</t>
@@ -1107,7 +1107,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1311,10 +1311,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1751,12 +1747,12 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.8166666666667" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.0333333333333" style="2" customWidth="1"/>
+    <col min="2" max="2" width="24.5" style="2" customWidth="1"/>
     <col min="3" max="4" width="13.625" style="2" customWidth="1"/>
     <col min="5" max="9" width="20.625" style="3" customWidth="1"/>
     <col min="10" max="10" width="15.25" style="3" customWidth="1"/>
     <col min="11" max="11" width="15.5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="23.6666666666667" style="2" customWidth="1"/>
+    <col min="12" max="12" width="27.25" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="48" customHeight="1" spans="1:12">
@@ -2058,10 +2054,10 @@
       <c r="H14" s="28"/>
       <c r="I14" s="28"/>
       <c r="J14" s="28"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="53" t="s">
+      <c r="K14" s="28" t="s">
         <v>50</v>
       </c>
+      <c r="L14" s="28"/>
     </row>
     <row r="15" ht="45" customHeight="1" spans="1:12">
       <c r="A15" s="29"/>
@@ -2072,8 +2068,8 @@
       <c r="F15" s="30"/>
       <c r="G15" s="30"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="54"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="53"/>
       <c r="K15" s="29"/>
       <c r="L15" s="29"/>
     </row>
@@ -2086,8 +2082,8 @@
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
       <c r="H16" s="32"/>
-      <c r="I16" s="55"/>
-      <c r="J16" s="55"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="54"/>
       <c r="K16" s="31"/>
       <c r="L16" s="31"/>
     </row>
@@ -2100,8 +2096,8 @@
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
-      <c r="I17" s="55"/>
-      <c r="J17" s="55"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="54"/>
       <c r="K17" s="31"/>
       <c r="L17" s="31"/>
     </row>
@@ -2119,7 +2115,7 @@
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" s="1" customFormat="1" ht="36" customHeight="1" spans="1:12">
+    <row r="19" s="1" customFormat="1" ht="43" customHeight="1" spans="1:12">
       <c r="A19" s="4" t="s">
         <v>51</v>
       </c>
@@ -2155,7 +2151,7 @@
         <v>5</v>
       </c>
       <c r="I20" s="34"/>
-      <c r="J20" s="56" t="s">
+      <c r="J20" s="55" t="s">
         <v>6</v>
       </c>
       <c r="K20" s="45"/>
@@ -2178,11 +2174,11 @@
       <c r="F21" s="15"/>
       <c r="G21" s="15"/>
       <c r="H21" s="15"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="58" t="s">
+      <c r="I21" s="56"/>
+      <c r="J21" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="K21" s="59" t="s">
+      <c r="K21" s="58" t="s">
         <v>56</v>
       </c>
       <c r="L21" s="11" t="s">
@@ -2208,7 +2204,7 @@
       <c r="J22" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="K22" s="60" t="s">
+      <c r="K22" s="59" t="s">
         <v>61</v>
       </c>
       <c r="L22" s="18" t="s">
@@ -2226,7 +2222,7 @@
       <c r="H23" s="19"/>
       <c r="I23" s="27"/>
       <c r="J23" s="21"/>
-      <c r="K23" s="60"/>
+      <c r="K23" s="59"/>
       <c r="L23" s="18"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="132" customHeight="1" spans="1:12">
@@ -2240,7 +2236,7 @@
       <c r="H24" s="38"/>
       <c r="I24" s="37"/>
       <c r="J24" s="21"/>
-      <c r="K24" s="60"/>
+      <c r="K24" s="59"/>
       <c r="L24" s="18"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="132" customHeight="1" spans="1:12">
@@ -2254,7 +2250,7 @@
       <c r="H25" s="38"/>
       <c r="I25" s="37"/>
       <c r="J25" s="21"/>
-      <c r="K25" s="60"/>
+      <c r="K25" s="59"/>
       <c r="L25" s="18"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="132" customHeight="1" spans="1:12">
@@ -2268,7 +2264,7 @@
       <c r="H26" s="38"/>
       <c r="I26" s="37"/>
       <c r="J26" s="21"/>
-      <c r="K26" s="60"/>
+      <c r="K26" s="59"/>
       <c r="L26" s="18"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="132" customHeight="1" spans="1:12">
@@ -2282,7 +2278,7 @@
       <c r="H27" s="38"/>
       <c r="I27" s="37"/>
       <c r="J27" s="21"/>
-      <c r="K27" s="60"/>
+      <c r="K27" s="59"/>
       <c r="L27" s="18"/>
     </row>
     <row r="28" ht="69" customHeight="1" spans="1:12">
@@ -2303,15 +2299,15 @@
       <c r="G28" s="43"/>
       <c r="H28" s="43"/>
       <c r="I28" s="43"/>
-      <c r="J28" s="61" t="s">
+      <c r="J28" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="K28" s="62"/>
-      <c r="L28" s="63" t="s">
+      <c r="K28" s="61"/>
+      <c r="L28" s="62" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="29" ht="51.95" customHeight="1" spans="1:12">
+    <row r="29" ht="60" customHeight="1" spans="1:12">
       <c r="A29" s="28" t="s">
         <v>49</v>
       </c>
@@ -2324,10 +2320,10 @@
       <c r="H29" s="28"/>
       <c r="I29" s="28"/>
       <c r="J29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="53" t="s">
+      <c r="K29" s="28" t="s">
         <v>50</v>
       </c>
+      <c r="L29" s="28"/>
     </row>
     <row r="30" ht="54.95" customHeight="1"/>
     <row r="31" ht="35.1" customHeight="1"/>
@@ -2343,7 +2339,7 @@
     <row r="41" ht="35.1" customHeight="1"/>
     <row r="42" ht="35.1" customHeight="1"/>
   </sheetData>
-  <mergeCells count="54">
+  <mergeCells count="56">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="F2:G2"/>
@@ -2365,7 +2361,8 @@
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="K13:L13"/>
-    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="K14:L14"/>
     <mergeCell ref="A19:L19"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="F20:G20"/>
@@ -2395,7 +2392,8 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:I28"/>
     <mergeCell ref="J28:K28"/>
-    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="K29:L29"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="L3:L4"/>
   </mergeCells>
@@ -2403,7 +2401,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2 C20 B12:D13"/>
   </dataValidations>
   <pageMargins left="0.472222222222222" right="0.354166666666667" top="0.196527777777778" bottom="0.236111111111111" header="0.236111111111111" footer="0.3"/>
-  <pageSetup paperSize="9" scale="37" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="35" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/TrafficTemplate.xlsx
@@ -82,7 +82,8 @@
     <t>{yearMonthDay}</t>
   </si>
   <si>
-    <t>财务收单编码：</t>
+    <t>财务收单
+编码：</t>
   </si>
   <si>
     <t>{finCode}</t>
@@ -229,10 +230,12 @@
     <t>具体内容</t>
   </si>
   <si>
-    <t>小计金额</t>
-  </si>
-  <si>
-    <t>进项税额</t>
+    <t>小计
+金额</t>
+  </si>
+  <si>
+    <t>进项
+税额</t>
   </si>
   <si>
     <t>{data2.prjNameNo}</t>
@@ -1322,8 +1325,8 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1469,7 +1472,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="635" y="15661005"/>
+          <a:off x="635" y="15775305"/>
           <a:ext cx="1997710" cy="588010"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1746,13 +1749,16 @@
   <dimension ref="A1:L42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="19.8166666666667" style="2" customWidth="1"/>
-    <col min="2" max="2" width="24.5" style="2" customWidth="1"/>
-    <col min="3" max="4" width="13.625" style="2" customWidth="1"/>
-    <col min="5" max="9" width="20.625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="15.25" style="3" customWidth="1"/>
-    <col min="11" max="11" width="15.5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="27.25" style="2" customWidth="1"/>
+    <col min="1" max="1" width="20.75" style="2" customWidth="1"/>
+    <col min="2" max="2" width="31.75" style="2" customWidth="1"/>
+    <col min="3" max="4" width="12.75" style="2" customWidth="1"/>
+    <col min="5" max="6" width="17.25" style="3" customWidth="1"/>
+    <col min="7" max="7" width="17.5" style="3" customWidth="1"/>
+    <col min="8" max="8" width="17.25" style="3" customWidth="1"/>
+    <col min="9" max="9" width="17" style="3" customWidth="1"/>
+    <col min="10" max="10" width="12" style="3" customWidth="1"/>
+    <col min="11" max="11" width="12.5" style="2" customWidth="1"/>
+    <col min="12" max="12" width="23.75" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="48" customHeight="1" spans="1:12">
@@ -1771,7 +1777,7 @@
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="48" customHeight="1" spans="1:12">
+    <row r="2" s="1" customFormat="1" ht="57" customHeight="1" spans="1:12">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -2131,7 +2137,7 @@
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" s="1" customFormat="1" ht="48" customHeight="1" spans="1:12">
+    <row r="20" s="1" customFormat="1" ht="55" customHeight="1" spans="1:12">
       <c r="A20" s="33" t="s">
         <v>1</v>
       </c>
@@ -2151,10 +2157,10 @@
         <v>5</v>
       </c>
       <c r="I20" s="34"/>
-      <c r="J20" s="55" t="s">
+      <c r="J20" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="K20" s="45"/>
+      <c r="K20" s="55"/>
       <c r="L20" s="46" t="s">
         <v>7</v>
       </c>
@@ -2401,7 +2407,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2 C20 B12:D13"/>
   </dataValidations>
   <pageMargins left="0.472222222222222" right="0.354166666666667" top="0.196527777777778" bottom="0.236111111111111" header="0.236111111111111" footer="0.3"/>
-  <pageSetup paperSize="9" scale="35" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="39" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
